--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;-0;;@"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -54,7 +56,7 @@
       <color rgb="00E87200"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -64,11 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00231815"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE4CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,17 +118,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,14 +513,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ① 대표 (유아용품 브랜드 대표님)</t>
+          <t>예시 ① 대표 (온라인몰 대표님, 지어낸 예시)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>진단 미팅과 워크샵에서 실제로 나온 말로 채운 판이에요.</t>
+          <t>지어낸 예시예요.</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>하루 합쳐 30분</t>
+          <t>0.5시간</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -602,15 +602,15 @@
           <t>마케팅 디자인 (배너 · 피드 · 이벤트 이미지)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>매주</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2시간</t>
         </is>
@@ -637,7 +637,7 @@
           <t>상세페이지 · 제품 디자인 (새 제품 오픈)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="5" t="n">
         <v>30</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>시즌엔 하루 종일</t>
+          <t>2시간 이상</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -668,20 +668,20 @@
           <t>인스타 · 릴스 마케팅</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>매주</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>2시간</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2단계</t>
         </is>
@@ -703,15 +703,15 @@
           <t>사업 계획 · 성과 숫자 정리</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>매달</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>2시간</t>
         </is>
@@ -734,15 +734,15 @@
           <t>외부 미팅 (광고사 · 콜라보 작가)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>매주</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>1시간</t>
         </is>
@@ -765,7 +765,7 @@
           <t>광고 성과 확인 (광고 운영은 외주)</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -773,9 +773,9 @@
           <t>매일</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>하루 5분</t>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.5시간</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -791,17 +791,17 @@
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B12" s="8">
-        <f>SUM(B5:B11)</f>
+        <f>IF(SUM(B5:B11)=0,"",SUM(B5:B11))</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IF(B12=100,"100 맞아요","합계를 100으로 맞춰요")</f>
+        <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -815,8 +815,8 @@
           <t>별표 세 개 넘기면 돌아오는 시간</t>
         </is>
       </c>
-      <c r="B13" s="6">
-        <f>SUMIF(G5:G11,"★*",B5:B11)</f>
+      <c r="B13" s="11">
+        <f>IF(SUMIF(G5:G11,"★*",B5:B11)=0,"",SUMIF(G5:G11,"★*",B5:B11))</f>
         <v/>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -828,14 +828,14 @@
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>그래서 이것부터: ★1 고객 문의 답장은 %가 10으로 크지 않지만 매일, 하루 30분, 1단계라 오늘 바로 AI에게 넘겨요. ★2 마케팅 디자인은 가이드 한 장을 먼저 만들고 넘겨요. ★3 마케팅은 채용할지 AI와 같이 할지 먼저 정해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>그래서 이것부터: ★1 고객 문의 답장은 %가 10으로 크지 않지만 매일, 0.5시간(30분), 1단계라 오늘 바로 AI에게 넘겨요. ★2 마케팅 디자인은 가이드 한 장을 먼저 만들고 넘겨요. ★3 마케팅은 채용할지 AI와 같이 할지 먼저 정해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>색칠한 칸은 표를 완성하려고 채운 설명용 값이에요. 고객 문의 10%와 하루 30분은 대표님이 직접 답한 값이에요.</t>
+          <t>지어낸 예시예요.</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,22 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="C12:E12"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1단계,2단계,3단계"</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"★1,★2,★3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.5시간,1시간,2시간"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1022,7 +1032,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1055,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,매주,매달"</formula1>
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1172,7 +1182,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>4시간</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1351,17 +1361,17 @@
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B12" s="8">
-        <f>SUM(B5:B11)</f>
+        <f>IF(SUM(B5:B11)=0,"",SUM(B5:B11))</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IF(B12=100,"100 맞아요","합계를 100으로 맞춰요")</f>
+        <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -1375,8 +1385,8 @@
           <t>별표 세 개 넘기면 돌아오는 시간</t>
         </is>
       </c>
-      <c r="B13" s="6">
-        <f>SUMIF(G5:G11,"★*",B5:B11)</f>
+      <c r="B13" s="11">
+        <f>IF(SUMIF(G5:G11,"★*",B5:B11)=0,"",SUMIF(G5:G11,"★*",B5:B11))</f>
         <v/>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -1399,12 +1409,22 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1단계,2단계,3단계"</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"★1,★2,★3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.5시간,1시간,2시간"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,7 +1586,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>4시간</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1632,7 +1652,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>4시간</t>
+          <t>2시간</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1710,17 +1730,17 @@
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B12" s="8">
-        <f>SUM(B5:B11)</f>
+        <f>IF(SUM(B5:B11)=0,"",SUM(B5:B11))</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IF(B12=100,"100 맞아요","합계를 100으로 맞춰요")</f>
+        <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -1734,8 +1754,8 @@
           <t>별표 세 개 넘기면 돌아오는 시간</t>
         </is>
       </c>
-      <c r="B13" s="6">
-        <f>SUMIF(G5:G11,"★*",B5:B11)</f>
+      <c r="B13" s="11">
+        <f>IF(SUMIF(G5:G11,"★*",B5:B11)=0,"",SUMIF(G5:G11,"★*",B5:B11))</f>
         <v/>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -1747,7 +1767,7 @@
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>그래서 이것부터: 문의 답장을 먼저 AI에게. 견적서와 정산은 %는 작아도 1단계라 같이 넘겨요. 정산은 매달 한 번이지만 한 번에 4시간이라 오래 붙잡는 일이에요. 돌아온 시간을 편집 작업과 새 고객 찾기에 써요.</t>
+          <t>그래서 이것부터: 문의 답장을 먼저 AI에게. 견적서와 정산은 %는 작아도 1단계라 같이 넘겨요. 정산은 매달 한 번이지만 한 번에 2시간이라 오래 붙잡는 일이에요. 돌아온 시간을 편집 작업과 새 고객 찾기에 써요.</t>
         </is>
       </c>
     </row>
@@ -1758,13 +1778,23 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1단계,2단계,3단계"</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
+    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"0.5시간,1시간,2시간"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -855,10 +855,10 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"0.5시간,1시간,2시간"</formula1>
+      <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
       <formula1>0</formula1>
@@ -1055,7 +1055,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1417,10 +1417,10 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"0.5시간,1시간,2시간"</formula1>
+      <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
       <formula1>0</formula1>
@@ -1786,10 +1786,10 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 몇 번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"0.5시간,1시간,2시간"</formula1>
+      <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="숫자만" error="0에서 100 사이 숫자만 적어요." type="whole" errorStyle="warning" operator="between">
       <formula1>0</formula1>

--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;-0;;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,10 @@
     <font>
       <b val="1"/>
       <color rgb="00E87200"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00231815"/>
     </font>
   </fonts>
   <fills count="4">
@@ -100,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +137,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -770,7 +775,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -825,10 +830,10 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>그래서 이것부터: ★1 고객 문의 답장은 %가 10으로 크지 않지만 매일, 0.5시간(30분), 1단계라 오늘 바로 AI에게 넘겨요. ★2 마케팅 디자인은 가이드 한 장을 먼저 만들고 넘겨요. ★3 마케팅은 채용할지 AI와 같이 할지 먼저 정해요.</t>
+          <t>그래서 이것부터: 3단계(상세페이지, 사업 계획, 외부 미팅)는 빼요. ★1 고객 문의 답장은 %가 10으로 크지 않지만 매일, 0.5시간(30분), 1단계라 먼저 별표예요. 남은 자리는 % 큰 순서라 ★2 마케팅 디자인(20), ★3 인스타 · 릴스 마케팅(15)이에요. 마케팅 디자인은 가이드 한 장을 먼저 만들고 넘기고, 인스타 · 릴스는 채용할지 AI와 같이 할지 먼저 정해요. 셋을 합치면 45예요.</t>
         </is>
       </c>
     </row>
@@ -875,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -963,98 +968,128 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>오후</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>제안서 핵심 내용 기획</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>매주 · 매달 한 번씩 하는 일 (따로 적어요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>언제</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>한 일</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>걸린 시간 (0.5 · 1 · 2시간)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>매주 / 매달</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>11시</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>어제 회의 회의록 정리 · 공유</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>주 4번</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>오후</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>제안서 핵심 내용 기획</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>다음 주 미팅 일정 조율</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>주 2번</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>금요일</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>주간 보고서 (숫자 모으기 + 정리)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>매일</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>오후</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>다음 주 미팅 일정 조율</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>주 2번</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>금요일</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>주간 보고서 (숫자 모으기 + 정리)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>매주</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>지어낸 예시: 마케팅팀 4년 차 직장인의 하루예요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1395,10 +1430,10 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>그래서 이것부터: 메일 답장과 회의록은 오늘 바로 AI에게, 보고서는 양식과 기준을 붙여 초안만 AI에게. 돌아온 40을 커리어에 남는 기획 · 제안서에 써요.</t>
+          <t>그래서 이것부터: 3단계(회의 참석, 제안서 · 기획 핵심)는 빼요. ★1 메일 확인 · 답장은 매일, 1시간, 1단계라 먼저 별표예요. 남은 자리는 % 큰 순서라 ★2 주간 보고서(15), ★3 회의록 정리(10)예요. 메일 답장과 회의록은 오늘 바로 AI에게, 보고서는 양식과 기준을 붙여 초안만 AI에게. 돌아온 40을 커리어에 남는 기획 · 제안서에 써요.</t>
         </is>
       </c>
     </row>

--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>시즌마다 몰아서</t>
+          <t>매달</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1088,8 +1088,11 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A15:D15"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D5:D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D11:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>

--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -78,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,55 @@
         <color rgb="00DCD1C1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,6 +182,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,7 +578,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>하는 일 (묶음)</t>
+          <t>하는 일</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -809,15 +855,15 @@
         <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>별표 세 개 넘기면 돌아오는 시간</t>
+          <t>TOP3 합계</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -880,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -968,131 +1014,175 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>어제 회의 회의록 정리 · 공유</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>주 4번</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>오후</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>자료 조사 · 정리</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>주 2번</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>오후</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>다음 주 미팅 일정 조율</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>주 2번</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>오후</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>제안서 핵심 내용 기획</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>매일</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>매주 · 매달 한 번씩 하는 일 (따로 적어요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>언제</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>한 일</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>걸린 시간 (0.5 · 1 · 2시간)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>매주 / 매달</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>11시</t>
+          <t>퇴근 전</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>어제 회의 회의록 정리 · 공유</t>
+          <t>퇴근 전 메일 답장</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>주 4번</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>오후</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>다음 주 미팅 일정 조율</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>주 2번</t>
-        </is>
-      </c>
-    </row>
+          <t>매일</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>매주 · 매달 한 번씩 하는 일 (따로 적어요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>언제</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>한 일</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>걸린 시간 (0.5 · 1 · 2시간)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>매주 / 매달</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>금요일</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>주간 보고서 (숫자 모으기 + 정리)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>매주</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>지어낸 예시: 마케팅팀 4년 차 직장인의 하루예요.</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D5:D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
-    <dataValidation sqref="D11:D13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1135,7 +1225,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>하는 일 (묶음)</t>
+          <t>하는 일</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1412,15 +1502,15 @@
         <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>별표 세 개 넘기면 돌아오는 시간</t>
+          <t>TOP3 합계</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -1504,7 +1594,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>하는 일 (묶음)</t>
+          <t>하는 일</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1781,15 +1871,15 @@
         <f>IF(B12="","",IF(B12=100,"100 맞아요","합계를 100으로 맞춰요"))</f>
         <v/>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>별표 세 개 넘기면 돌아오는 시간</t>
+          <t>TOP3 합계</t>
         </is>
       </c>
       <c r="B13" s="11">

--- a/01-02-02/top3-form-example.xlsx
+++ b/01-02-02/top3-form-example.xlsx
@@ -564,7 +564,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ① 대표 (온라인몰 대표님, 지어낸 예시)</t>
+          <t>예시1 대표 (온라인몰 대표님, 지어낸 예시)</t>
         </is>
       </c>
     </row>
@@ -575,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -876,6 +877,7 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -906,7 +908,7 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
@@ -926,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -949,6 +951,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -967,7 +970,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>매일 / 매주 / 매달</t>
+          <t>매일 / 주 몇 번</t>
         </is>
       </c>
     </row>
@@ -1169,21 +1172,20 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번"</formula1>
     </dataValidation>
     <dataValidation sqref="D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매주,매달"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1211,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ② 직장인 (마케팅팀 4년 차) 2장</t>
+          <t>예시2 직장인 (마케팅팀 4년 차) 2장</t>
         </is>
       </c>
     </row>
@@ -1222,6 +1224,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1523,6 +1526,7 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1549,7 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
@@ -1580,7 +1584,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>예시 ③ 프리랜서 (영상 편집) 2장</t>
+          <t>예시3 프리랜서 (영상 편집) 2장</t>
         </is>
       </c>
     </row>
@@ -1591,6 +1595,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1892,6 +1897,7 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -1914,7 +1920,7 @@
       <formula1>"★1,★2,★3"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"매일,주 1번,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
+      <formula1>"매일,주 2번,주 3번,주 4번,주 5번,매주,매달"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0.5시간,1시간,2시간,2시간 이상"</formula1>
